--- a/data/sales-10.xlsx
+++ b/data/sales-10.xlsx
@@ -833,31 +833,31 @@
         </is>
       </c>
       <c r="B12" s="65">
-        <v>60723</v>
+        <v>55333</v>
       </c>
       <c r="C12" s="66">
-        <v>10.00</v>
-      </c>
-      <c r="D12" s="65">
-        <v>0</v>
+        <v>38.00</v>
+      </c>
+      <c r="D12" s="66">
+        <v>2102.00</v>
       </c>
       <c r="E12" s="66">
-        <v>60713.00</v>
+        <v>53193.00</v>
       </c>
       <c r="F12" s="66">
         <v>0.00</v>
       </c>
       <c r="G12" s="66">
-        <v>60713.00</v>
+        <v>53193.00</v>
       </c>
       <c r="H12" s="66">
         <v>0.00</v>
       </c>
-      <c r="I12" s="66">
-        <v>0.00</v>
-      </c>
-      <c r="J12" s="66">
-        <v>0.00</v>
+      <c r="I12" s="65">
+        <v>0</v>
+      </c>
+      <c r="J12" s="65">
+        <v>0</v>
       </c>
       <c r="K12" s="65">
         <v>0</v>
@@ -866,7 +866,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="66">
-        <v>60713.00</v>
+        <v>53193.00</v>
       </c>
       <c r="N12" s="66">
         <v>0.00</v>
@@ -875,11 +875,11 @@
         <v>0.00</v>
       </c>
       <c r="P12" s="65">
-        <v>502</v>
+        <v>362</v>
       </c>
       <c t="inlineStr" r="Q12">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
         </is>
       </c>
     </row>
@@ -947,31 +947,31 @@
         </is>
       </c>
       <c r="B14" s="65">
-        <v>55333</v>
+        <v>60723</v>
       </c>
       <c r="C14" s="66">
-        <v>38.00</v>
-      </c>
-      <c r="D14" s="66">
-        <v>2102.00</v>
+        <v>10.00</v>
+      </c>
+      <c r="D14" s="65">
+        <v>0</v>
       </c>
       <c r="E14" s="66">
-        <v>53193.00</v>
+        <v>60713.00</v>
       </c>
       <c r="F14" s="66">
         <v>0.00</v>
       </c>
       <c r="G14" s="66">
-        <v>53193.00</v>
+        <v>60713.00</v>
       </c>
       <c r="H14" s="66">
         <v>0.00</v>
       </c>
-      <c r="I14" s="65">
-        <v>0</v>
-      </c>
-      <c r="J14" s="65">
-        <v>0</v>
+      <c r="I14" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J14" s="66">
+        <v>0.00</v>
       </c>
       <c r="K14" s="65">
         <v>0</v>
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="66">
-        <v>53193.00</v>
+        <v>60713.00</v>
       </c>
       <c r="N14" s="66">
         <v>0.00</v>
@@ -989,11 +989,11 @@
         <v>0.00</v>
       </c>
       <c r="P14" s="65">
-        <v>362</v>
+        <v>502</v>
       </c>
       <c t="inlineStr" r="Q14">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
         </is>
       </c>
     </row>
@@ -1175,31 +1175,31 @@
         </is>
       </c>
       <c r="B18" s="65">
-        <v>57823</v>
+        <v>49539</v>
       </c>
       <c r="C18" s="66">
-        <v>0.00</v>
+        <v>180.00</v>
       </c>
       <c r="D18" s="66">
-        <v>2286.00</v>
+        <v>100.00</v>
       </c>
       <c r="E18" s="66">
-        <v>55537.00</v>
+        <v>49259.00</v>
       </c>
       <c r="F18" s="66">
         <v>0.00</v>
       </c>
       <c r="G18" s="66">
-        <v>55537.00</v>
+        <v>49259.00</v>
       </c>
       <c r="H18" s="66">
         <v>0.00</v>
       </c>
-      <c r="I18" s="66">
-        <v>0.00</v>
-      </c>
-      <c r="J18" s="66">
-        <v>0.00</v>
+      <c r="I18" s="65">
+        <v>0</v>
+      </c>
+      <c r="J18" s="65">
+        <v>0</v>
       </c>
       <c r="K18" s="65">
         <v>0</v>
@@ -1208,7 +1208,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="66">
-        <v>55537.00</v>
+        <v>49259.00</v>
       </c>
       <c r="N18" s="66">
         <v>0.00</v>
@@ -1217,11 +1217,11 @@
         <v>0.00</v>
       </c>
       <c r="P18" s="65">
-        <v>361</v>
+        <v>424</v>
       </c>
       <c t="inlineStr" r="Q18">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
         </is>
       </c>
     </row>
@@ -1289,31 +1289,31 @@
         </is>
       </c>
       <c r="B20" s="65">
-        <v>49539</v>
+        <v>57823</v>
       </c>
       <c r="C20" s="66">
-        <v>180.00</v>
+        <v>0.00</v>
       </c>
       <c r="D20" s="66">
-        <v>100.00</v>
+        <v>2286.00</v>
       </c>
       <c r="E20" s="66">
-        <v>49259.00</v>
+        <v>55537.00</v>
       </c>
       <c r="F20" s="66">
         <v>0.00</v>
       </c>
       <c r="G20" s="66">
-        <v>49259.00</v>
+        <v>55537.00</v>
       </c>
       <c r="H20" s="66">
         <v>0.00</v>
       </c>
-      <c r="I20" s="65">
-        <v>0</v>
-      </c>
-      <c r="J20" s="65">
-        <v>0</v>
+      <c r="I20" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J20" s="66">
+        <v>0.00</v>
       </c>
       <c r="K20" s="65">
         <v>0</v>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="66">
-        <v>49259.00</v>
+        <v>55537.00</v>
       </c>
       <c r="N20" s="66">
         <v>0.00</v>
@@ -1331,11 +1331,11 @@
         <v>0.00</v>
       </c>
       <c r="P20" s="65">
-        <v>424</v>
+        <v>361</v>
       </c>
       <c t="inlineStr" r="Q20">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
         </is>
       </c>
     </row>
@@ -1346,31 +1346,31 @@
         </is>
       </c>
       <c r="B21" s="65">
-        <v>58917</v>
+        <v>53127</v>
       </c>
       <c r="C21" s="66">
-        <v>40.00</v>
+        <v>0.00</v>
       </c>
       <c r="D21" s="66">
-        <v>300.00</v>
+        <v>2104.00</v>
       </c>
       <c r="E21" s="66">
-        <v>58577.00</v>
+        <v>51023.00</v>
       </c>
       <c r="F21" s="66">
         <v>0.00</v>
       </c>
       <c r="G21" s="66">
-        <v>58577.00</v>
+        <v>51023.00</v>
       </c>
       <c r="H21" s="66">
         <v>0.00</v>
       </c>
-      <c r="I21" s="66">
-        <v>0.00</v>
-      </c>
-      <c r="J21" s="66">
-        <v>0.00</v>
+      <c r="I21" s="65">
+        <v>0</v>
+      </c>
+      <c r="J21" s="65">
+        <v>0</v>
       </c>
       <c r="K21" s="65">
         <v>0</v>
@@ -1379,7 +1379,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="66">
-        <v>58577.00</v>
+        <v>51023.00</v>
       </c>
       <c r="N21" s="66">
         <v>0.00</v>
@@ -1388,11 +1388,11 @@
         <v>0.00</v>
       </c>
       <c r="P21" s="65">
-        <v>482</v>
+        <v>363</v>
       </c>
       <c t="inlineStr" r="Q21">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
         </is>
       </c>
     </row>
@@ -1460,31 +1460,31 @@
         </is>
       </c>
       <c r="B23" s="65">
-        <v>53127</v>
+        <v>58917</v>
       </c>
       <c r="C23" s="66">
-        <v>0.00</v>
+        <v>40.00</v>
       </c>
       <c r="D23" s="66">
-        <v>2104.00</v>
+        <v>300.00</v>
       </c>
       <c r="E23" s="66">
-        <v>51023.00</v>
+        <v>58577.00</v>
       </c>
       <c r="F23" s="66">
         <v>0.00</v>
       </c>
       <c r="G23" s="66">
-        <v>51023.00</v>
+        <v>58577.00</v>
       </c>
       <c r="H23" s="66">
         <v>0.00</v>
       </c>
-      <c r="I23" s="65">
-        <v>0</v>
-      </c>
-      <c r="J23" s="65">
-        <v>0</v>
+      <c r="I23" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J23" s="66">
+        <v>0.00</v>
       </c>
       <c r="K23" s="65">
         <v>0</v>
@@ -1493,7 +1493,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="66">
-        <v>51023.00</v>
+        <v>58577.00</v>
       </c>
       <c r="N23" s="66">
         <v>0.00</v>
@@ -1502,11 +1502,11 @@
         <v>0.00</v>
       </c>
       <c r="P23" s="65">
-        <v>363</v>
+        <v>482</v>
       </c>
       <c t="inlineStr" r="Q23">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
         </is>
       </c>
     </row>
@@ -1859,31 +1859,31 @@
         </is>
       </c>
       <c r="B30" s="65">
-        <v>49971</v>
+        <v>40176</v>
       </c>
       <c r="C30" s="66">
-        <v>40.00</v>
+        <v>0.00</v>
       </c>
       <c r="D30" s="66">
-        <v>100.00</v>
+        <v>1624.00</v>
       </c>
       <c r="E30" s="66">
-        <v>49831.00</v>
+        <v>38552.00</v>
       </c>
       <c r="F30" s="66">
         <v>0.00</v>
       </c>
       <c r="G30" s="66">
-        <v>49831.00</v>
+        <v>38552.00</v>
       </c>
       <c r="H30" s="66">
         <v>0.00</v>
       </c>
       <c r="I30" s="66">
-        <v>0.00</v>
+        <v>200.00</v>
       </c>
       <c r="J30" s="66">
-        <v>0.00</v>
+        <v>194.00</v>
       </c>
       <c r="K30" s="65">
         <v>0</v>
@@ -1892,20 +1892,20 @@
         <v>0</v>
       </c>
       <c r="M30" s="66">
-        <v>49831.00</v>
+        <v>38358.00</v>
       </c>
       <c r="N30" s="66">
         <v>0.00</v>
       </c>
       <c r="O30" s="66">
-        <v>0.00</v>
+        <v>38.00</v>
       </c>
       <c r="P30" s="65">
-        <v>432</v>
+        <v>265</v>
       </c>
       <c t="inlineStr" r="Q30">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
         </is>
       </c>
     </row>
@@ -1973,31 +1973,31 @@
         </is>
       </c>
       <c r="B32" s="65">
-        <v>40176</v>
+        <v>49971</v>
       </c>
       <c r="C32" s="66">
-        <v>0.00</v>
+        <v>40.00</v>
       </c>
       <c r="D32" s="66">
-        <v>1624.00</v>
+        <v>100.00</v>
       </c>
       <c r="E32" s="66">
-        <v>38552.00</v>
+        <v>49831.00</v>
       </c>
       <c r="F32" s="66">
         <v>0.00</v>
       </c>
       <c r="G32" s="66">
-        <v>38552.00</v>
+        <v>49831.00</v>
       </c>
       <c r="H32" s="66">
         <v>0.00</v>
       </c>
       <c r="I32" s="66">
-        <v>200.00</v>
+        <v>0.00</v>
       </c>
       <c r="J32" s="66">
-        <v>194.00</v>
+        <v>0.00</v>
       </c>
       <c r="K32" s="65">
         <v>0</v>
@@ -2006,20 +2006,20 @@
         <v>0</v>
       </c>
       <c r="M32" s="66">
-        <v>38358.00</v>
+        <v>49831.00</v>
       </c>
       <c r="N32" s="66">
         <v>0.00</v>
       </c>
       <c r="O32" s="66">
-        <v>38.00</v>
+        <v>0.00</v>
       </c>
       <c r="P32" s="65">
-        <v>265</v>
+        <v>432</v>
       </c>
       <c t="inlineStr" r="Q32">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
         </is>
       </c>
     </row>
@@ -2030,22 +2030,22 @@
         </is>
       </c>
       <c r="B33" s="65">
-        <v>47925</v>
+        <v>53905</v>
       </c>
       <c r="C33" s="66">
-        <v>38.00</v>
+        <v>40.00</v>
       </c>
       <c r="D33" s="66">
-        <v>2316.00</v>
+        <v>300.00</v>
       </c>
       <c r="E33" s="66">
-        <v>45571.00</v>
+        <v>53565.00</v>
       </c>
       <c r="F33" s="66">
         <v>0.00</v>
       </c>
       <c r="G33" s="66">
-        <v>45571.00</v>
+        <v>53565.00</v>
       </c>
       <c r="H33" s="66">
         <v>0.00</v>
@@ -2063,7 +2063,7 @@
         <v>0</v>
       </c>
       <c r="M33" s="66">
-        <v>45571.00</v>
+        <v>53565.00</v>
       </c>
       <c r="N33" s="66">
         <v>0.00</v>
@@ -2072,11 +2072,11 @@
         <v>0.00</v>
       </c>
       <c r="P33" s="65">
-        <v>294</v>
+        <v>459</v>
       </c>
       <c t="inlineStr" r="Q33">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
         </is>
       </c>
     </row>
@@ -2087,31 +2087,31 @@
         </is>
       </c>
       <c r="B34" s="65">
-        <v>53905</v>
+        <v>21962</v>
       </c>
       <c r="C34" s="66">
-        <v>40.00</v>
+        <v>0.00</v>
       </c>
       <c r="D34" s="66">
-        <v>300.00</v>
+        <v>207.50</v>
       </c>
       <c r="E34" s="66">
-        <v>53565.00</v>
+        <v>21754.50</v>
       </c>
       <c r="F34" s="66">
         <v>0.00</v>
       </c>
       <c r="G34" s="66">
-        <v>53565.00</v>
+        <v>21754.50</v>
       </c>
       <c r="H34" s="66">
         <v>0.00</v>
       </c>
-      <c r="I34" s="66">
-        <v>0.00</v>
-      </c>
-      <c r="J34" s="66">
-        <v>0.00</v>
+      <c r="I34" s="65">
+        <v>0</v>
+      </c>
+      <c r="J34" s="65">
+        <v>0</v>
       </c>
       <c r="K34" s="65">
         <v>0</v>
@@ -2120,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="M34" s="66">
-        <v>53565.00</v>
+        <v>21754.50</v>
       </c>
       <c r="N34" s="66">
         <v>0.00</v>
@@ -2129,11 +2129,11 @@
         <v>0.00</v>
       </c>
       <c r="P34" s="65">
-        <v>459</v>
+        <v>106</v>
       </c>
       <c t="inlineStr" r="Q34">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
         </is>
       </c>
     </row>
@@ -2144,31 +2144,31 @@
         </is>
       </c>
       <c r="B35" s="65">
-        <v>21962</v>
+        <v>47925</v>
       </c>
       <c r="C35" s="66">
-        <v>0.00</v>
+        <v>38.00</v>
       </c>
       <c r="D35" s="66">
-        <v>207.50</v>
+        <v>2316.00</v>
       </c>
       <c r="E35" s="66">
-        <v>21754.50</v>
+        <v>45571.00</v>
       </c>
       <c r="F35" s="66">
         <v>0.00</v>
       </c>
       <c r="G35" s="66">
-        <v>21754.50</v>
+        <v>45571.00</v>
       </c>
       <c r="H35" s="66">
         <v>0.00</v>
       </c>
-      <c r="I35" s="65">
-        <v>0</v>
-      </c>
-      <c r="J35" s="65">
-        <v>0</v>
+      <c r="I35" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J35" s="66">
+        <v>0.00</v>
       </c>
       <c r="K35" s="65">
         <v>0</v>
@@ -2177,7 +2177,7 @@
         <v>0</v>
       </c>
       <c r="M35" s="66">
-        <v>21754.50</v>
+        <v>45571.00</v>
       </c>
       <c r="N35" s="66">
         <v>0.00</v>
@@ -2186,11 +2186,11 @@
         <v>0.00</v>
       </c>
       <c r="P35" s="65">
-        <v>106</v>
+        <v>294</v>
       </c>
       <c t="inlineStr" r="Q35">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
         </is>
       </c>
     </row>
@@ -2372,31 +2372,31 @@
         </is>
       </c>
       <c r="B39" s="65">
-        <v>53690</v>
+        <v>47155</v>
       </c>
       <c r="C39" s="66">
         <v>0.00</v>
       </c>
       <c r="D39" s="66">
-        <v>100.00</v>
+        <v>1374.00</v>
       </c>
       <c r="E39" s="66">
-        <v>53590.00</v>
+        <v>45781.00</v>
       </c>
       <c r="F39" s="66">
         <v>0.00</v>
       </c>
       <c r="G39" s="66">
-        <v>53590.00</v>
+        <v>45781.00</v>
       </c>
       <c r="H39" s="66">
         <v>0.00</v>
       </c>
-      <c r="I39" s="66">
-        <v>0.00</v>
-      </c>
-      <c r="J39" s="66">
-        <v>0.00</v>
+      <c r="I39" s="65">
+        <v>0</v>
+      </c>
+      <c r="J39" s="65">
+        <v>0</v>
       </c>
       <c r="K39" s="65">
         <v>0</v>
@@ -2405,7 +2405,7 @@
         <v>0</v>
       </c>
       <c r="M39" s="66">
-        <v>53590.00</v>
+        <v>45781.00</v>
       </c>
       <c r="N39" s="66">
         <v>0.00</v>
@@ -2414,11 +2414,11 @@
         <v>0.00</v>
       </c>
       <c r="P39" s="65">
-        <v>449</v>
+        <v>298</v>
       </c>
       <c t="inlineStr" r="Q39">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
         </is>
       </c>
     </row>
@@ -2429,22 +2429,22 @@
         </is>
       </c>
       <c r="B40" s="65">
-        <v>19124</v>
+        <v>53690</v>
       </c>
       <c r="C40" s="66">
         <v>0.00</v>
       </c>
       <c r="D40" s="66">
-        <v>200.00</v>
+        <v>100.00</v>
       </c>
       <c r="E40" s="66">
-        <v>18924.00</v>
+        <v>53590.00</v>
       </c>
       <c r="F40" s="66">
         <v>0.00</v>
       </c>
       <c r="G40" s="66">
-        <v>18924.00</v>
+        <v>53590.00</v>
       </c>
       <c r="H40" s="66">
         <v>0.00</v>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="66">
-        <v>18924.00</v>
+        <v>53590.00</v>
       </c>
       <c r="N40" s="66">
         <v>0.00</v>
@@ -2471,11 +2471,11 @@
         <v>0.00</v>
       </c>
       <c r="P40" s="65">
-        <v>93</v>
+        <v>449</v>
       </c>
       <c t="inlineStr" r="Q40">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
         </is>
       </c>
     </row>
@@ -2486,31 +2486,31 @@
         </is>
       </c>
       <c r="B41" s="65">
-        <v>47155</v>
+        <v>19124</v>
       </c>
       <c r="C41" s="66">
         <v>0.00</v>
       </c>
       <c r="D41" s="66">
-        <v>1374.00</v>
+        <v>200.00</v>
       </c>
       <c r="E41" s="66">
-        <v>45781.00</v>
+        <v>18924.00</v>
       </c>
       <c r="F41" s="66">
         <v>0.00</v>
       </c>
       <c r="G41" s="66">
-        <v>45781.00</v>
+        <v>18924.00</v>
       </c>
       <c r="H41" s="66">
         <v>0.00</v>
       </c>
-      <c r="I41" s="65">
-        <v>0</v>
-      </c>
-      <c r="J41" s="65">
-        <v>0</v>
+      <c r="I41" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J41" s="66">
+        <v>0.00</v>
       </c>
       <c r="K41" s="65">
         <v>0</v>
@@ -2519,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="M41" s="66">
-        <v>45781.00</v>
+        <v>18924.00</v>
       </c>
       <c r="N41" s="66">
         <v>0.00</v>
@@ -2528,11 +2528,11 @@
         <v>0.00</v>
       </c>
       <c r="P41" s="65">
-        <v>298</v>
+        <v>93</v>
       </c>
       <c t="inlineStr" r="Q41">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
         </is>
       </c>
     </row>
@@ -3398,22 +3398,22 @@
         </is>
       </c>
       <c r="B57" s="65">
-        <v>14425</v>
+        <v>45912</v>
       </c>
       <c r="C57" s="66">
-        <v>70.00</v>
+        <v>0.00</v>
       </c>
       <c r="D57" s="66">
-        <v>200.00</v>
+        <v>1944.00</v>
       </c>
       <c r="E57" s="66">
-        <v>14155.00</v>
+        <v>43968.00</v>
       </c>
       <c r="F57" s="66">
         <v>0.00</v>
       </c>
       <c r="G57" s="66">
-        <v>14155.00</v>
+        <v>43968.00</v>
       </c>
       <c r="H57" s="66">
         <v>0.00</v>
@@ -3431,7 +3431,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="66">
-        <v>14155.00</v>
+        <v>43968.00</v>
       </c>
       <c r="N57" s="66">
         <v>0.00</v>
@@ -3440,11 +3440,11 @@
         <v>0.00</v>
       </c>
       <c r="P57" s="65">
-        <v>148</v>
+        <v>349</v>
       </c>
       <c t="inlineStr" r="Q57">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
         </is>
       </c>
     </row>
@@ -3512,22 +3512,22 @@
         </is>
       </c>
       <c r="B59" s="65">
-        <v>45912</v>
+        <v>14425</v>
       </c>
       <c r="C59" s="66">
-        <v>0.00</v>
+        <v>70.00</v>
       </c>
       <c r="D59" s="66">
-        <v>1944.00</v>
+        <v>200.00</v>
       </c>
       <c r="E59" s="66">
-        <v>43968.00</v>
+        <v>14155.00</v>
       </c>
       <c r="F59" s="66">
         <v>0.00</v>
       </c>
       <c r="G59" s="66">
-        <v>43968.00</v>
+        <v>14155.00</v>
       </c>
       <c r="H59" s="66">
         <v>0.00</v>
@@ -3545,7 +3545,7 @@
         <v>0</v>
       </c>
       <c r="M59" s="66">
-        <v>43968.00</v>
+        <v>14155.00</v>
       </c>
       <c r="N59" s="66">
         <v>0.00</v>
@@ -3554,11 +3554,11 @@
         <v>0.00</v>
       </c>
       <c r="P59" s="65">
-        <v>349</v>
+        <v>148</v>
       </c>
       <c t="inlineStr" r="Q59">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
         </is>
       </c>
     </row>
@@ -3734,59 +3734,743 @@
       </c>
     </row>
     <row r="63">
-      <c t="inlineStr" r="A63" s="2">
+      <c t="inlineStr" r="A63">
+        <is>
+          <t xml:space="preserve">21/10/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="65">
+        <v>13642</v>
+      </c>
+      <c r="C63" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D63" s="66">
+        <v>100.00</v>
+      </c>
+      <c r="E63" s="66">
+        <v>13542.00</v>
+      </c>
+      <c r="F63" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G63" s="66">
+        <v>13542.00</v>
+      </c>
+      <c r="H63" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I63" s="65">
+        <v>0</v>
+      </c>
+      <c r="J63" s="65">
+        <v>0</v>
+      </c>
+      <c r="K63" s="65">
+        <v>0</v>
+      </c>
+      <c r="L63" s="65">
+        <v>0</v>
+      </c>
+      <c r="M63" s="66">
+        <v>13542.00</v>
+      </c>
+      <c r="N63" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O63" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P63" s="65">
+        <v>156</v>
+      </c>
+      <c t="inlineStr" r="Q63">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c t="inlineStr" r="A64">
+        <is>
+          <t xml:space="preserve">21/10/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="65">
+        <v>20386</v>
+      </c>
+      <c r="C64" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D64" s="66">
+        <v>205.00</v>
+      </c>
+      <c r="E64" s="66">
+        <v>20181.00</v>
+      </c>
+      <c r="F64" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G64" s="66">
+        <v>20181.00</v>
+      </c>
+      <c r="H64" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I64" s="65">
+        <v>0</v>
+      </c>
+      <c r="J64" s="65">
+        <v>0</v>
+      </c>
+      <c r="K64" s="65">
+        <v>0</v>
+      </c>
+      <c r="L64" s="65">
+        <v>0</v>
+      </c>
+      <c r="M64" s="66">
+        <v>20181.00</v>
+      </c>
+      <c r="N64" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O64" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P64" s="65">
+        <v>100</v>
+      </c>
+      <c t="inlineStr" r="Q64">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c t="inlineStr" r="A65">
+        <is>
+          <t xml:space="preserve">21/10/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="65">
+        <v>56950</v>
+      </c>
+      <c r="C65" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D65" s="66">
+        <v>2204.00</v>
+      </c>
+      <c r="E65" s="66">
+        <v>54746.00</v>
+      </c>
+      <c r="F65" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G65" s="66">
+        <v>54746.00</v>
+      </c>
+      <c r="H65" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I65" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="J65" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="K65" s="65">
+        <v>0</v>
+      </c>
+      <c r="L65" s="65">
+        <v>0</v>
+      </c>
+      <c r="M65" s="66">
+        <v>54746.00</v>
+      </c>
+      <c r="N65" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O65" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P65" s="65">
+        <v>382</v>
+      </c>
+      <c t="inlineStr" r="Q65">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c t="inlineStr" r="A66">
+        <is>
+          <t xml:space="preserve">22/10/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="65">
+        <v>17832</v>
+      </c>
+      <c r="C66" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D66" s="66">
+        <v>200.00</v>
+      </c>
+      <c r="E66" s="66">
+        <v>17632.00</v>
+      </c>
+      <c r="F66" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G66" s="66">
+        <v>17632.00</v>
+      </c>
+      <c r="H66" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I66" s="65">
+        <v>0</v>
+      </c>
+      <c r="J66" s="65">
+        <v>0</v>
+      </c>
+      <c r="K66" s="65">
+        <v>0</v>
+      </c>
+      <c r="L66" s="65">
+        <v>0</v>
+      </c>
+      <c r="M66" s="66">
+        <v>17632.00</v>
+      </c>
+      <c r="N66" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O66" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P66" s="65">
+        <v>186</v>
+      </c>
+      <c t="inlineStr" r="Q66">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c t="inlineStr" r="A67">
+        <is>
+          <t xml:space="preserve">22/10/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="65">
+        <v>16670</v>
+      </c>
+      <c r="C67" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D67" s="66">
+        <v>180.00</v>
+      </c>
+      <c r="E67" s="66">
+        <v>16490.00</v>
+      </c>
+      <c r="F67" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G67" s="66">
+        <v>16490.00</v>
+      </c>
+      <c r="H67" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I67" s="65">
+        <v>0</v>
+      </c>
+      <c r="J67" s="65">
+        <v>0</v>
+      </c>
+      <c r="K67" s="65">
+        <v>0</v>
+      </c>
+      <c r="L67" s="65">
+        <v>0</v>
+      </c>
+      <c r="M67" s="66">
+        <v>16490.00</v>
+      </c>
+      <c r="N67" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O67" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P67" s="65">
+        <v>87</v>
+      </c>
+      <c t="inlineStr" r="Q67">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c t="inlineStr" r="A68">
+        <is>
+          <t xml:space="preserve">22/10/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="65">
+        <v>45187</v>
+      </c>
+      <c r="C68" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D68" s="66">
+        <v>2020.00</v>
+      </c>
+      <c r="E68" s="66">
+        <v>43167.00</v>
+      </c>
+      <c r="F68" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G68" s="66">
+        <v>43167.00</v>
+      </c>
+      <c r="H68" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I68" s="65">
+        <v>0</v>
+      </c>
+      <c r="J68" s="65">
+        <v>0</v>
+      </c>
+      <c r="K68" s="65">
+        <v>0</v>
+      </c>
+      <c r="L68" s="65">
+        <v>0</v>
+      </c>
+      <c r="M68" s="66">
+        <v>43167.00</v>
+      </c>
+      <c r="N68" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O68" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P68" s="65">
+        <v>317</v>
+      </c>
+      <c t="inlineStr" r="Q68">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c t="inlineStr" r="A69">
+        <is>
+          <t xml:space="preserve">23/10/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="65">
+        <v>16356</v>
+      </c>
+      <c r="C69" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D69" s="65">
+        <v>0</v>
+      </c>
+      <c r="E69" s="66">
+        <v>16356.00</v>
+      </c>
+      <c r="F69" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G69" s="66">
+        <v>16356.00</v>
+      </c>
+      <c r="H69" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I69" s="65">
+        <v>0</v>
+      </c>
+      <c r="J69" s="65">
+        <v>0</v>
+      </c>
+      <c r="K69" s="65">
+        <v>0</v>
+      </c>
+      <c r="L69" s="65">
+        <v>0</v>
+      </c>
+      <c r="M69" s="66">
+        <v>16356.00</v>
+      </c>
+      <c r="N69" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O69" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P69" s="65">
+        <v>179</v>
+      </c>
+      <c t="inlineStr" r="Q69">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c t="inlineStr" r="A70">
+        <is>
+          <t xml:space="preserve">23/10/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="65">
+        <v>17598</v>
+      </c>
+      <c r="C70" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D70" s="66">
+        <v>130.00</v>
+      </c>
+      <c r="E70" s="66">
+        <v>17468.00</v>
+      </c>
+      <c r="F70" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G70" s="66">
+        <v>17468.00</v>
+      </c>
+      <c r="H70" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I70" s="65">
+        <v>0</v>
+      </c>
+      <c r="J70" s="65">
+        <v>0</v>
+      </c>
+      <c r="K70" s="65">
+        <v>0</v>
+      </c>
+      <c r="L70" s="65">
+        <v>0</v>
+      </c>
+      <c r="M70" s="66">
+        <v>17468.00</v>
+      </c>
+      <c r="N70" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O70" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P70" s="65">
+        <v>86</v>
+      </c>
+      <c t="inlineStr" r="Q70">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c t="inlineStr" r="A71">
+        <is>
+          <t xml:space="preserve">23/10/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="65">
+        <v>50286</v>
+      </c>
+      <c r="C71" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D71" s="66">
+        <v>2014.00</v>
+      </c>
+      <c r="E71" s="66">
+        <v>48272.00</v>
+      </c>
+      <c r="F71" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G71" s="66">
+        <v>48272.00</v>
+      </c>
+      <c r="H71" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I71" s="65">
+        <v>0</v>
+      </c>
+      <c r="J71" s="65">
+        <v>0</v>
+      </c>
+      <c r="K71" s="65">
+        <v>0</v>
+      </c>
+      <c r="L71" s="65">
+        <v>0</v>
+      </c>
+      <c r="M71" s="66">
+        <v>48272.00</v>
+      </c>
+      <c r="N71" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O71" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P71" s="65">
+        <v>330</v>
+      </c>
+      <c t="inlineStr" r="Q71">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c t="inlineStr" r="A72">
+        <is>
+          <t xml:space="preserve">24/10/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="65">
+        <v>19474</v>
+      </c>
+      <c r="C72" s="66">
+        <v>70.00</v>
+      </c>
+      <c r="D72" s="66">
+        <v>200.00</v>
+      </c>
+      <c r="E72" s="66">
+        <v>19204.00</v>
+      </c>
+      <c r="F72" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G72" s="66">
+        <v>19204.00</v>
+      </c>
+      <c r="H72" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I72" s="65">
+        <v>0</v>
+      </c>
+      <c r="J72" s="65">
+        <v>0</v>
+      </c>
+      <c r="K72" s="65">
+        <v>0</v>
+      </c>
+      <c r="L72" s="65">
+        <v>0</v>
+      </c>
+      <c r="M72" s="66">
+        <v>19204.00</v>
+      </c>
+      <c r="N72" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O72" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P72" s="65">
+        <v>202</v>
+      </c>
+      <c t="inlineStr" r="Q72">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c t="inlineStr" r="A73">
+        <is>
+          <t xml:space="preserve">24/10/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="65">
+        <v>17984</v>
+      </c>
+      <c r="C73" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D73" s="66">
+        <v>235.00</v>
+      </c>
+      <c r="E73" s="66">
+        <v>17749.00</v>
+      </c>
+      <c r="F73" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G73" s="66">
+        <v>17749.00</v>
+      </c>
+      <c r="H73" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I73" s="65">
+        <v>0</v>
+      </c>
+      <c r="J73" s="65">
+        <v>0</v>
+      </c>
+      <c r="K73" s="65">
+        <v>0</v>
+      </c>
+      <c r="L73" s="65">
+        <v>0</v>
+      </c>
+      <c r="M73" s="66">
+        <v>17749.00</v>
+      </c>
+      <c r="N73" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O73" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P73" s="65">
+        <v>95</v>
+      </c>
+      <c t="inlineStr" r="Q73">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c t="inlineStr" r="A74">
+        <is>
+          <t xml:space="preserve">24/10/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="65">
+        <v>49938</v>
+      </c>
+      <c r="C74" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="D74" s="66">
+        <v>2310.00</v>
+      </c>
+      <c r="E74" s="66">
+        <v>47628.00</v>
+      </c>
+      <c r="F74" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="G74" s="66">
+        <v>47628.00</v>
+      </c>
+      <c r="H74" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="I74" s="65">
+        <v>0</v>
+      </c>
+      <c r="J74" s="65">
+        <v>0</v>
+      </c>
+      <c r="K74" s="65">
+        <v>0</v>
+      </c>
+      <c r="L74" s="65">
+        <v>0</v>
+      </c>
+      <c r="M74" s="66">
+        <v>47628.00</v>
+      </c>
+      <c r="N74" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="O74" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="P74" s="65">
+        <v>325</v>
+      </c>
+      <c t="inlineStr" r="Q74">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - สาขาบางแสน</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c t="inlineStr" r="A75" s="2">
         <is>
           <t xml:space="preserve">Total</t>
         </is>
       </c>
-      <c r="B63" s="2">
-        <v>2271651.00</v>
-      </c>
-      <c r="C63" s="2">
-        <v>1304.00</v>
-      </c>
-      <c r="D63" s="2">
-        <v>42265.50</v>
-      </c>
-      <c r="E63" s="2">
-        <v>2228081.50</v>
-      </c>
-      <c r="F63" s="2">
-        <v>0.00</v>
-      </c>
-      <c r="G63" s="2">
-        <v>2228081.50</v>
-      </c>
-      <c r="H63" s="2">
-        <v>0.00</v>
-      </c>
-      <c r="I63" s="2">
+      <c r="B75" s="2">
+        <v>2613954.00</v>
+      </c>
+      <c r="C75" s="2">
+        <v>1374.00</v>
+      </c>
+      <c r="D75" s="2">
+        <v>52063.50</v>
+      </c>
+      <c r="E75" s="2">
+        <v>2560516.50</v>
+      </c>
+      <c r="F75" s="2">
+        <v>0.00</v>
+      </c>
+      <c r="G75" s="2">
+        <v>2560516.50</v>
+      </c>
+      <c r="H75" s="2">
+        <v>0.00</v>
+      </c>
+      <c r="I75" s="2">
         <v>900.00</v>
       </c>
-      <c r="J63" s="2">
+      <c r="J75" s="2">
         <v>894.00</v>
       </c>
-      <c r="K63" s="2">
-        <v>0.00</v>
-      </c>
-      <c r="L63" s="2">
-        <v>0.00</v>
-      </c>
-      <c r="M63" s="2">
-        <v>2227187.50</v>
-      </c>
-      <c r="N63" s="2">
-        <v>0.00</v>
-      </c>
-      <c r="O63" s="2">
+      <c r="K75" s="2">
+        <v>0.00</v>
+      </c>
+      <c r="L75" s="2">
+        <v>0.00</v>
+      </c>
+      <c r="M75" s="2">
+        <v>2559622.50</v>
+      </c>
+      <c r="N75" s="2">
+        <v>0.00</v>
+      </c>
+      <c r="O75" s="2">
         <v>114.00</v>
       </c>
-      <c r="P63" s="2">
-        <v>15919.00</v>
+      <c r="P75" s="2">
+        <v>18364.00</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q62"/>
+  <autoFilter ref="A2:Q74"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
